--- a/docs/demo/dian/facturas_recibidas_enero_2025.xlsx
+++ b/docs/demo/dian/facturas_recibidas_enero_2025.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>901234567</t>
+          <t>901777888</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>901234567</t>
+          <t>901777888</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ba8c5b8b5dd139a3e08b00b3c1d5367f4c1e8f315debdeff23d164da11b3d725a2216fa5b49f78614c02ff72eb76932f</t>
+          <t>c36d07cb81ebfc9b389377ceb4ce115eaad3eaa06493e20e4cded18030c4731040cf41c925e64cf703b1e0de30d048e1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>901234567</t>
+          <t>901777888</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
